--- a/Gravedigger2026/Assets/ConfigTables/Excel/制造_额外装备配置表_Manufacture_ExtraEquipmentConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/制造_额外装备配置表_Manufacture_ExtraEquipmentConfig.xlsx
@@ -625,7 +625,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MaxHP_14|MoveSpeed_0.30000000000000004|Strength_2|Agility_0|Intelligence_1</t>
+          <t>MaxHP_14|MoveSpeed_0.3|Strength_2|Agility_0|Intelligence_1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -658,7 +658,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MaxHP_16|MoveSpeed_0.35000000000000003|Strength_0|Agility_1|Intelligence_2</t>
+          <t>MaxHP_16|MoveSpeed_0.35|Strength_0|Agility_1|Intelligence_2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -827,7 +827,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MaxHP_26|MoveSpeed_0.6000000000000001|Strength_2|Agility_0|Intelligence_1</t>
+          <t>MaxHP_26|MoveSpeed_0.6|Strength_2|Agility_0|Intelligence_1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
